--- a/project2-sll-structuring/SLL_Structuring_Model.xlsx
+++ b/project2-sll-structuring/SLL_Structuring_Model.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. Borrower Profile" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. KPI Tracker" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. SPT Calibration" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Margin Ratchet Calculator" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="0. Borrower Profile" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1. KPI Tracker" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2. SPT Calibration" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3. Margin Ratchet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. Utilisation Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. Economics &amp; Caveats" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,12 +22,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="+0.0;-0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000&quot;%&quot;"/>
-    <numFmt numFmtId="167" formatCode="£#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000"/>
+    <numFmt numFmtId="167" formatCode="+#,##0.0;-#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,10 +42,8 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00C62828"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -51,11 +51,23 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002E7D32"/>
       <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="000000CC"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A7A4A"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
       <i val="1"/>
-      <color rgb="00555555"/>
+      <color rgb="00C62828"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -83,11 +95,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -97,160 +109,74 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFCDD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFF9C4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C8E6C9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -612,161 +538,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SLL Structuring Model — Albion Industrials plc (Hypothetical)</t>
+          <t>SLL STRUCTURING MODEL — ALBION INDUSTRIALS PLC (HYPOTHETICAL)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Fictional entity for illustrative purposes only. No real company financial data is used anywhere in this model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+          <t>Fictional entity, for illustrative purposes only. No real company financial data is used anywhere in this model. All targets, rates and costs are illustrative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>UK Heavy Industrials (Steel &amp; Construction Materials)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Revenue (hypothetical)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>£2.8bn</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>EBITDA margin (hypothetical)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Existing debt (hypothetical)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>£650m revolving credit facility</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Credit rating (hypothetical)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>BBB– (investment grade)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Scope 1+2 intensity baseline (hypothetical)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Scope 1+2 intensity (baseline)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>310 tCO2e per £m revenue</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Renewable energy share baseline (hypothetical)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Renewable energy share (baseline)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Reference framework</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>LMA/APLMA/LSTA Sustainability-Linked Loan Principles (2023)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>How to use this workbook</t>
-        </is>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>1. Borrower Profile — hypothetical baseline data.
-2. KPI Tracker — baseline vs current vs target for each KPI, with live progress %.
-3. SPT Calibration &amp; Glide Path — annual interim targets between baseline and 2028 SPT.
-4. Margin Ratchet Calculator — enter number of SPTs met to see the adjusted margin and annual interest cost; all inputs (facility size, base margin, SONIA) are editable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>HOW TO USE THIS WORKBOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Yellow cells are inputs; everything else is a live formula. Sheet 1 tracks KPI progress. Sheet 2 calibrates the SPTs and derives the carbon glide path. Sheet 3 prices the facility — change the utilisation or any rate and the scenario table recalculates. Sheet 4 shows how the ratchet benefit varies with drawdown, and Sheet 5 asks whether the structure pays for itself at all.</t>
+        </is>
+      </c>
+    </row>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>REPRODUCIBILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>This workbook is generated by scripts/build_model.py from the calculations in scripts/sll.py — it is not hand-maintained. Rebuild it with: python scripts/build_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A16:B20"/>
-    <mergeCell ref="A3:B3"/>
+  <mergeCells count="4">
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="A23:B24"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A17:B20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -778,21 +717,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KPI Tracker — Baseline vs Current vs Target</t>
+          <t>KPI TRACKER — BASELINE VS CURRENT VS TARGET</t>
         </is>
       </c>
     </row>
@@ -824,109 +763,99 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Progress to Target</t>
+          <t>Progress to target</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Carbon intensity</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>tCO2e per £m revenue (Scope 1+2)</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="4" t="n">
         <v>310</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>267</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="4" t="n">
         <v>217</v>
       </c>
-      <c r="F4" s="11">
-        <f>(C4-D4)/(C4-E4)</f>
+      <c r="F4" s="10">
+        <f>(D4-C4)/(E4-C4)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Renewable energy share</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>% of electricity from renewables</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <f>(D5-C5)/(E5-C5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Supply chain audit coverage</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>% tier-1 suppliers audited to ESG standards</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>52</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <f>(D6-C6)/(E6-C6)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Note: 'Current (2026, hypothetical)' is the only editable (yellow) input — illustrative interim progress, not real reported data. Progress % recalculates live.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Only the yellow 'Current' column is editable — illustrative interim progress, not reported data. Progress is computed as (current − baseline) / (target − baseline), so it reads correctly for carbon intensity (which must fall) and for the two shares (which must rise).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:F10"/>
   </mergeCells>
-  <conditionalFormatting sqref="F4:F6">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
-      <formula>0.4</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="between" dxfId="1">
-      <formula>0.4</formula>
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="2">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -937,20 +866,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sustainability Performance Target Calibration</t>
+          <t>SUSTAINABILITY PERFORMANCE TARGET CALIBRATION</t>
         </is>
       </c>
     </row>
@@ -967,7 +896,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Target Year</t>
+          <t>Target year</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -977,148 +906,212 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Benchmark Source</t>
+          <t>Benchmark source</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Carbon intensity</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>310 tCO2e/£m rev</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="7" t="n">
         <v>2028</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>&lt;=217 tCO2e/£m rev (-30%)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>SBTi 1.5C near-term pathway (Industrials)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Renewable share</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="5" t="n">
         <v>2028</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>&gt;=60%</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>UK Climate Change Committee 6th Carbon Budget</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Supply chain audit</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="7" t="n">
         <v>2027</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>&gt;=80%</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>LMA SLLP best practice</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>A 30% carbon intensity reduction over four years (~7% per year) is consistent with the SBTi near-term pathway for the Industrials sector.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Carbon Intensity Glide Path (linear, baseline → SPT)</t>
-        </is>
-      </c>
-    </row>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>A 30% carbon intensity reduction over four years (~7%/yr) is consistent with the SBTi near-term pathway for Industrials. SLLP guidance requires SPTs to be a material improvement on baseline and benchmarked against a recognised pathway rather than set by the borrower alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>CARBON INTENSITY GLIDE PATH (linear, baseline → SPT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>310</v>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>← editable</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2028 SPT</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>286.8</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>263.5</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>240.2</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>217</v>
-      </c>
-    </row>
+    <row r="16">
+      <c r="A16" s="13">
+        <f>$B$12+($B$13-$B$12)*0/4</f>
+        <v/>
+      </c>
+      <c r="B16" s="14">
+        <f>$B$12+($B$13-$B$12)*1/4</f>
+        <v/>
+      </c>
+      <c r="C16" s="14">
+        <f>$B$12+($B$13-$B$12)*2/4</f>
+        <v/>
+      </c>
+      <c r="D16" s="14">
+        <f>$B$12+($B$13-$B$12)*3/4</f>
+        <v/>
+      </c>
+      <c r="E16" s="13">
+        <f>$B$12+($B$13-$B$12)*4/4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Annual reduction required (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="15">
+        <f>B16/A16-1</f>
+        <v/>
+      </c>
+      <c r="C18" s="15">
+        <f>C16/B16-1</f>
+        <v/>
+      </c>
+      <c r="D18" s="15">
+        <f>D16/C16-1</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
+        <f>E16/D16-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>The glide path is formula-driven from the two yellow cells, so changing the baseline or the SPT moves every interim target. Interim SPTs matter because the ratchet is tested annually, not once at maturity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A20:E21"/>
+    <mergeCell ref="A8:E9"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1130,301 +1123,940 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Margin Ratchet Calculator (Illustrative)</t>
+          <t>MARGIN RATCHET CALCULATOR (ILLUSTRATIVE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>A revolving facility is rarely fully drawn, and the ratchet applies only to the drawn margin — so the benefit scales with utilisation. The undrawn balance carries a commitment fee, conventionally a fixed share of the margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Facility size (£m)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Base margin (bps over SONIA)</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SONIA reference rate (%)</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Utilisation (% of facility drawn)</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Commitment fee (% of margin)</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Full step (bps) — all 3 SPTs met</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Partial step (bps) — 2 of 3 met</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Step-up (bps) — 0 met</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Annual verification cost (£m)</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SPTs met this period (0–3)</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Drawn balance (£m)</t>
+        </is>
+      </c>
+      <c r="D17" s="14">
+        <f>'3. Margin Ratchet'!$D$5*'3. Margin Ratchet'!$D$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Undrawn commitment (£m)</t>
+        </is>
+      </c>
+      <c r="D18" s="14">
+        <f>'3. Margin Ratchet'!$D$5*(1-'3. Margin Ratchet'!$D$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Commitment fee (bps)</t>
+        </is>
+      </c>
+      <c r="D19" s="14">
+        <f>'3. Margin Ratchet'!$D$6*'3. Margin Ratchet'!$D$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Margin adjustment (bps)</t>
+        </is>
+      </c>
+      <c r="D20" s="20">
+        <f>IF('3. Margin Ratchet'!$D$14=3,-'3. Margin Ratchet'!$D$10,IF('3. Margin Ratchet'!$D$14=2,-'3. Margin Ratchet'!$D$11,IF('3. Margin Ratchet'!$D$14=1,0,'3. Margin Ratchet'!$D$12)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Adjusted margin (bps)</t>
+        </is>
+      </c>
+      <c r="D21" s="14">
+        <f>'3. Margin Ratchet'!$D$6+$D$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>All-in rate on drawn (%)</t>
+        </is>
+      </c>
+      <c r="D22" s="21">
+        <f>'3. Margin Ratchet'!$D$7+$D$21/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Interest on drawn (£m)</t>
+        </is>
+      </c>
+      <c r="D23" s="21">
+        <f>$D$17*$D$22/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Commitment fee cost (£m)</t>
+        </is>
+      </c>
+      <c r="D24" s="21">
+        <f>$D$18*$D$19/100/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL ANNUAL COST (£m)</t>
+        </is>
+      </c>
+      <c r="D25" s="22">
+        <f>$D$23+$D$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>SCENARIO COMPARISON (at the inputs above)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>SPTs met</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Margin adj (bps)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Margin (bps)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Interest on drawn (£m)</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Commitment fee (£m)</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Total cost (£m)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>vs no adjustment (£k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="20">
+        <f>IF(A29=3,-'3. Margin Ratchet'!$D$10,IF(A29=2,-'3. Margin Ratchet'!$D$11,IF(A29=1,0,'3. Margin Ratchet'!$D$12)))</f>
+        <v/>
+      </c>
+      <c r="C29" s="14">
+        <f>'3. Margin Ratchet'!$D$6+B29</f>
+        <v/>
+      </c>
+      <c r="D29" s="21">
+        <f>$D$17*('3. Margin Ratchet'!$D$7+C29/100)/100</f>
+        <v/>
+      </c>
+      <c r="E29" s="21">
+        <f>$D$24</f>
+        <v/>
+      </c>
+      <c r="F29" s="21">
+        <f>D29+E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="20">
+        <f>$D$17*B29/100/100*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="23">
+        <f>IF(A30=3,-'3. Margin Ratchet'!$D$10,IF(A30=2,-'3. Margin Ratchet'!$D$11,IF(A30=1,0,'3. Margin Ratchet'!$D$12)))</f>
+        <v/>
+      </c>
+      <c r="C30" s="24">
+        <f>'3. Margin Ratchet'!$D$6+B30</f>
+        <v/>
+      </c>
+      <c r="D30" s="25">
+        <f>$D$17*('3. Margin Ratchet'!$D$7+C30/100)/100</f>
+        <v/>
+      </c>
+      <c r="E30" s="25">
+        <f>$D$24</f>
+        <v/>
+      </c>
+      <c r="F30" s="25">
+        <f>D30+E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="23">
+        <f>$D$17*B30/100/100*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="20">
+        <f>IF(A31=3,-'3. Margin Ratchet'!$D$10,IF(A31=2,-'3. Margin Ratchet'!$D$11,IF(A31=1,0,'3. Margin Ratchet'!$D$12)))</f>
+        <v/>
+      </c>
+      <c r="C31" s="14">
+        <f>'3. Margin Ratchet'!$D$6+B31</f>
+        <v/>
+      </c>
+      <c r="D31" s="21">
+        <f>$D$17*('3. Margin Ratchet'!$D$7+C31/100)/100</f>
+        <v/>
+      </c>
+      <c r="E31" s="21">
+        <f>$D$24</f>
+        <v/>
+      </c>
+      <c r="F31" s="21">
+        <f>D31+E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="20">
+        <f>$D$17*B31/100/100*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" s="23">
+        <f>IF(A32=3,-'3. Margin Ratchet'!$D$10,IF(A32=2,-'3. Margin Ratchet'!$D$11,IF(A32=1,0,'3. Margin Ratchet'!$D$12)))</f>
+        <v/>
+      </c>
+      <c r="C32" s="24">
+        <f>'3. Margin Ratchet'!$D$6+B32</f>
+        <v/>
+      </c>
+      <c r="D32" s="25">
+        <f>$D$17*('3. Margin Ratchet'!$D$7+C32/100)/100</f>
+        <v/>
+      </c>
+      <c r="E32" s="25">
+        <f>$D$24</f>
+        <v/>
+      </c>
+      <c r="F32" s="25">
+        <f>D32+E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="23">
+        <f>$D$17*B32/100/100*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>The commitment fee is identical across scenarios because this structure ratchets only the drawn margin. Some SLLs also ratchet the commitment fee pro rata, which would widen the spread between scenarios by roughly the commitment-fee percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F3"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A34:G35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RATCHET BENEFIT BY UTILISATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The headline ratchet saving assumes the facility is fully drawn. It is not a fixed benefit: it is proportional to the drawn balance, while the verification cost that earns it is fixed. This is the table that decides whether an SLL is worth doing on price alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Utilisation</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Drawn (£m)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Total cost at base margin (£m)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Max annual saving (£k)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Verification cost (£k)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Net benefit (£k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" s="14">
+        <f>'3. Margin Ratchet'!$D$5*A6</f>
+        <v/>
+      </c>
+      <c r="C6" s="26">
+        <f>B6*('3. Margin Ratchet'!$D$7+'3. Margin Ratchet'!$D$6/100)/100+('3. Margin Ratchet'!$D$5-B6)*('3. Margin Ratchet'!$D$6*'3. Margin Ratchet'!$D$9)/100/100</f>
+        <v/>
+      </c>
+      <c r="D6" s="14">
+        <f>B6*'3. Margin Ratchet'!$D$10/100/100*1000</f>
+        <v/>
+      </c>
+      <c r="E6" s="14">
+        <f>'3. Margin Ratchet'!$D$13*1000</f>
+        <v/>
+      </c>
+      <c r="F6" s="27">
+        <f>D6-E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B7" s="24">
+        <f>'3. Margin Ratchet'!$D$5*A7</f>
+        <v/>
+      </c>
+      <c r="C7" s="29">
+        <f>B7*('3. Margin Ratchet'!$D$7+'3. Margin Ratchet'!$D$6/100)/100+('3. Margin Ratchet'!$D$5-B7)*('3. Margin Ratchet'!$D$6*'3. Margin Ratchet'!$D$9)/100/100</f>
+        <v/>
+      </c>
+      <c r="D7" s="24">
+        <f>B7*'3. Margin Ratchet'!$D$10/100/100*1000</f>
+        <v/>
+      </c>
+      <c r="E7" s="24">
+        <f>'3. Margin Ratchet'!$D$13*1000</f>
+        <v/>
+      </c>
+      <c r="F7" s="30">
+        <f>D7-E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B8" s="14">
+        <f>'3. Margin Ratchet'!$D$5*A8</f>
+        <v/>
+      </c>
+      <c r="C8" s="26">
+        <f>B8*('3. Margin Ratchet'!$D$7+'3. Margin Ratchet'!$D$6/100)/100+('3. Margin Ratchet'!$D$5-B8)*('3. Margin Ratchet'!$D$6*'3. Margin Ratchet'!$D$9)/100/100</f>
+        <v/>
+      </c>
+      <c r="D8" s="14">
+        <f>B8*'3. Margin Ratchet'!$D$10/100/100*1000</f>
+        <v/>
+      </c>
+      <c r="E8" s="14">
+        <f>'3. Margin Ratchet'!$D$13*1000</f>
+        <v/>
+      </c>
+      <c r="F8" s="27">
+        <f>D8-E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B9" s="24">
+        <f>'3. Margin Ratchet'!$D$5*A9</f>
+        <v/>
+      </c>
+      <c r="C9" s="29">
+        <f>B9*('3. Margin Ratchet'!$D$7+'3. Margin Ratchet'!$D$6/100)/100+('3. Margin Ratchet'!$D$5-B9)*('3. Margin Ratchet'!$D$6*'3. Margin Ratchet'!$D$9)/100/100</f>
+        <v/>
+      </c>
+      <c r="D9" s="24">
+        <f>B9*'3. Margin Ratchet'!$D$10/100/100*1000</f>
+        <v/>
+      </c>
+      <c r="E9" s="24">
+        <f>'3. Margin Ratchet'!$D$13*1000</f>
+        <v/>
+      </c>
+      <c r="F9" s="30">
+        <f>D9-E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B10" s="14">
+        <f>'3. Margin Ratchet'!$D$5*A10</f>
+        <v/>
+      </c>
+      <c r="C10" s="26">
+        <f>B10*('3. Margin Ratchet'!$D$7+'3. Margin Ratchet'!$D$6/100)/100+('3. Margin Ratchet'!$D$5-B10)*('3. Margin Ratchet'!$D$6*'3. Margin Ratchet'!$D$9)/100/100</f>
+        <v/>
+      </c>
+      <c r="D10" s="14">
+        <f>B10*'3. Margin Ratchet'!$D$10/100/100*1000</f>
+        <v/>
+      </c>
+      <c r="E10" s="14">
+        <f>'3. Margin Ratchet'!$D$13*1000</f>
+        <v/>
+      </c>
+      <c r="F10" s="27">
+        <f>D10-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="24">
+        <f>'3. Margin Ratchet'!$D$5*A11</f>
+        <v/>
+      </c>
+      <c r="C11" s="29">
+        <f>B11*('3. Margin Ratchet'!$D$7+'3. Margin Ratchet'!$D$6/100)/100+('3. Margin Ratchet'!$D$5-B11)*('3. Margin Ratchet'!$D$6*'3. Margin Ratchet'!$D$9)/100/100</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>B11*'3. Margin Ratchet'!$D$10/100/100*1000</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>'3. Margin Ratchet'!$D$13*1000</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
+        <f>D11-E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>BREAK-EVEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Break-even utilisation</t>
+        </is>
+      </c>
+      <c r="B14" s="10">
+        <f>'3. Margin Ratchet'!$D$13/('3. Margin Ratchet'!$D$5*'3. Margin Ratchet'!$D$10/100/100)</f>
+        <v/>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Below this drawdown the best-case ratchet saving does not cover the verification cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>At the default inputs the break-even is about 21% utilisation. A borrower expecting to keep the facility largely undrawn — which is the normal use of an RCF as a liquidity backstop — gets little or no pricing benefit, and the case for the SLL has to rest on signalling, investor relations or internal accountability rather than on cost. That is a recognised criticism of the instrument and it is worth being explicit about rather than quoting the full-drawdown figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F3"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A16:F18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IS THE STRUCTURE WORTH IT?</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Inputs</t>
+          <t>AT THE DEFAULT INPUTS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Facility size (£m)</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="15" t="n">
-        <v>650</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Base margin (bps over SONIA)</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="16" t="n">
-        <v>120</v>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Facility size</t>
+        </is>
+      </c>
+      <c r="B5" s="31">
+        <f>'3. Margin Ratchet'!$D$5</f>
+        <v/>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Committed amount</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>SONIA rate (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="17" t="n">
-        <v>4.25</v>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Assumed utilisation</t>
+        </is>
+      </c>
+      <c r="B6" s="32">
+        <f>'3. Margin Ratchet'!$D$8</f>
+        <v/>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Share drawn on average</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Full step (bps) — all 3 SPTs met</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="18" t="n">
-        <v>7.5</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Best-case annual saving</t>
+        </is>
+      </c>
+      <c r="B7" s="14">
+        <f>$B$5*$B$6*'3. Margin Ratchet'!$D$10/100/100*1000</f>
+        <v/>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>£k</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>All 3 SPTs met, on the drawn balance</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Partial step (bps) — 2 of 3 SPTs met</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="18" t="n">
-        <v>2.5</v>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Annual verification cost</t>
+        </is>
+      </c>
+      <c r="B8" s="14">
+        <f>'3. Margin Ratchet'!$D$13*1000</f>
+        <v/>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>£k</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>ISAE 3000 assurance; fixed, does not scale with drawdown</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Step-up (bps) — 0 SPTs met</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="18" t="n">
-        <v>7.5</v>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Net annual benefit</t>
+        </is>
+      </c>
+      <c r="B9" s="27">
+        <f>$B$7-$B$8</f>
+        <v/>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>£k</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Negative means the structure costs more than it returns</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Number of SPTs met this period (0–3)</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="16" t="n">
-        <v>3</v>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Break-even utilisation</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
+        <f>'3. Margin Ratchet'!$D$13/('3. Margin Ratchet'!$D$5*'3. Margin Ratchet'!$D$10/100/100)</f>
+        <v/>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Drawdown at which saving = verification cost</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Live Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Margin adjustment (bps)</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="19">
-        <f>IF(D10=3,-D7,IF(D10=2,-D8,IF(D10=1,0,D9)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Adjusted margin (bps over SONIA)</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="20">
-        <f>D5+D13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>All-in rate (%)</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="21">
-        <f>D6+D14/100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Annual interest cost (£m, full facility drawn)</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="22">
-        <f>D4*D15/100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Scenario Comparison (illustrative, at inputs above)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>SPTs met</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Margin adj (bps)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Adjusted margin (bps)</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Annual interest cost (£m)</t>
+          <t>WHAT THIS MODEL DELIBERATELY DOES NOT CLAIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>• The ratchet is priced on the drawn margin only. Structures that also ratchet the commitment fee would show a larger spread.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>• A ±7.5bps step is small relative to credit-spread volatility, so in practice the SLL label is unlikely to be the binding factor in the borrower's cost of capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>• No discounting: these are single-year figures. Over a five-year facility the saving is roughly five times the annual number, less the verification cost each year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>• Verification cost is a single illustrative input. Real assurance costs vary with scope, and the first year is usually dearer than later ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>• The two-way ratchet assumes the step-up is genuinely enforced. A step-down-only structure gives the borrower a free option and is the main greenwashing channel the SLLP guidance targets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>• KPI selection, not pricing, is where the real integrity risk sits: a material KPI with an unambitious SPT prices identically to a demanding one in this model.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="19">
-        <f>IF(3=3,-D7,IF(3=2,-D8,IF(3=1,0,D9)))</f>
-        <v/>
-      </c>
-      <c r="C20" s="20">
-        <f>D5+B20</f>
-        <v/>
-      </c>
-      <c r="D20" s="22">
-        <f>D4*(D6+C20/100)/100</f>
-        <v/>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>VERIFICATION &amp; REPORTING</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="23">
-        <f>IF(2=3,-D7,IF(2=2,-D8,IF(2=1,0,D9)))</f>
-        <v/>
-      </c>
-      <c r="C21" s="24">
-        <f>D5+B21</f>
-        <v/>
-      </c>
-      <c r="D21" s="25">
-        <f>D4*(D6+C21/100)/100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="19">
-        <f>IF(1=3,-D7,IF(1=2,-D8,IF(1=1,0,D9)))</f>
-        <v/>
-      </c>
-      <c r="C22" s="20">
-        <f>D5+B22</f>
-        <v/>
-      </c>
-      <c r="D22" s="22">
-        <f>D4*(D6+C22/100)/100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="B23" s="23">
-        <f>IF(0=3,-D7,IF(0=2,-D8,IF(0=1,0,D9)))</f>
-        <v/>
-      </c>
-      <c r="C23" s="24">
-        <f>D5+B23</f>
-        <v/>
-      </c>
-      <c r="D23" s="25">
-        <f>D4*(D6+C23/100)/100</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>External verifier: Big 4 assurance or a specialist ESG verifier. Reporting: annual sustainability report plus a loan anniversary compliance letter. Assurance standard: ISAE 3000 / AA1000AS. KPI data sourced from SECR disclosures (energy and carbon) and the REGO certificate registry (renewable share) — both UK statutory or registry-based, so no paid data subscription is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>All figures illustrative only — hypothetical borrower, facility, and rates. Yellow cells are editable inputs; all totals recalculate automatically.</t>
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>All figures illustrative — hypothetical borrower, facility and rates.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A10:C10"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A21:D23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="D10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Enter a whole number 0–3." type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>3</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project2-sll-structuring/SLL_Structuring_Model.xlsx
+++ b/project2-sll-structuring/SLL_Structuring_Model.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="0. Borrower Profile" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1. KPI Tracker" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2. SPT Calibration" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3. Margin Ratchet" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4. Utilisation Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5. Economics &amp; Caveats" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. Borrower Profile" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. KPI Tracker" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. SPT Calibration" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Margin Ratchet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Utilisation Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Economics &amp; Caveats" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>LMA/APLMA/LSTA Sustainability-Linked Loan Principles (2023)</t>
+          <t>LMA/APLMA/LSTA Sustainability-Linked Loan Principles (2023 edition; revised March 2025)</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Yellow cells are inputs; everything else is a live formula. Sheet 1 tracks KPI progress. Sheet 2 calibrates the SPTs and derives the carbon glide path. Sheet 3 prices the facility — change the utilisation or any rate and the scenario table recalculates. Sheet 4 shows how the ratchet benefit varies with drawdown, and Sheet 5 asks whether the structure pays for itself at all.</t>
+          <t>Yellow cells are inputs; everything else is a live formula. Sheet 1 tracks KPI progress. Sheet 2 sets illustrative SPTs and derives linear glide paths for all three KPIs. Sheet 3 prices the facility — the number of SPTs met is a separate input there, not driven by Sheet 1. Sheet 4 shows how the ratchet benefit varies with drawdown, and Sheet 5 compares the facility with an equivalent conventional revolver.</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -726,6 +726,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -758,12 +759,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Target / SPT (2028)</t>
+          <t>Target / SPT</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Progress to target</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Target year</t>
         </is>
       </c>
     </row>
@@ -791,6 +797,9 @@
         <f>(D4-C4)/(E4-C4)</f>
         <v/>
       </c>
+      <c r="G4" s="4" t="n">
+        <v>2028</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -816,6 +825,9 @@
         <f>(D5-C5)/(E5-C5)</f>
         <v/>
       </c>
+      <c r="G5" s="4" t="n">
+        <v>2028</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -841,11 +853,14 @@
         <f>(D6-C6)/(E6-C6)</f>
         <v/>
       </c>
+      <c r="G6" s="4" t="n">
+        <v>2027</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Only the yellow 'Current' column is editable — illustrative interim progress, not reported data. Progress is computed as (current − baseline) / (target − baseline), so it reads correctly for carbon intensity (which must fall) and for the two shares (which must rise).</t>
+          <t>Only the yellow 'Current' column is editable — illustrative interim progress, not reported data. Progress is computed as (current − baseline) / (target − baseline), so it reads correctly for carbon intensity (which must fall) and for the two shares (which must rise). Progress here does not set pricing: the number of SPTs met is entered separately on Sheet 3.</t>
         </is>
       </c>
     </row>
@@ -853,7 +868,7 @@
     <row r="10"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A8:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -866,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -906,7 +921,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Benchmark source</t>
+          <t>Informed by (alignment not established)</t>
         </is>
       </c>
     </row>
@@ -931,7 +946,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>SBTi 1.5C near-term pathway (Industrials)</t>
+          <t>SBTi near-term criteria</t>
         </is>
       </c>
     </row>
@@ -956,7 +971,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>UK Climate Change Committee 6th Carbon Budget</t>
+          <t>UK CCC Sixth Carbon Budget (December 2020)</t>
         </is>
       </c>
     </row>
@@ -981,14 +996,14 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>LMA SLLP best practice</t>
+          <t>LMA SLLP guidance on ambition</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>A 30% carbon intensity reduction over four years (~7%/yr) is consistent with the SBTi near-term pathway for Industrials. SLLP guidance requires SPTs to be a material improvement on baseline and benchmarked against a recognised pathway rather than set by the borrower alone.</t>
+          <t>Illustrative targets informed by the frameworks named; alignment has not been independently established. SBTi accepts Scope 1+2 intensity targets only when modelled on an approved 1.5C sector pathway applicable to the company, so a chosen percentage is not evidence of alignment.</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1092,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Annual reduction required (%)</t>
+          <t>Change on the prior year (%) — the linear path moves 7.5% of the baseline a year, so this rate rises over time</t>
         </is>
       </c>
     </row>
@@ -1099,19 +1114,169 @@
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>The glide path is formula-driven from the two yellow cells, so changing the baseline or the SPT moves every interim target. Interim SPTs matter because the ratchet is tested annually, not once at maturity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Equivalent constant annual rate</t>
+        </is>
+      </c>
+      <c r="B19" s="15">
+        <f>($B$13/$B$12)^(1/4)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>The glide paths are formula-driven from the yellow endpoint cells, so changing a baseline or an SPT moves every interim target. Interim SPTs matter because the ratchet is tested annually, not once at maturity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>RENEWABLE ELECTRICITY SHARE (%) — 2024 → 2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13">
+        <f>$B$25+($D$25-$B$25)*0/4</f>
+        <v/>
+      </c>
+      <c r="B27" s="14">
+        <f>$B$25+($D$25-$B$25)*1/4</f>
+        <v/>
+      </c>
+      <c r="C27" s="14">
+        <f>$B$25+($D$25-$B$25)*2/4</f>
+        <v/>
+      </c>
+      <c r="D27" s="14">
+        <f>$B$25+($D$25-$B$25)*3/4</f>
+        <v/>
+      </c>
+      <c r="E27" s="13">
+        <f>$B$25+($D$25-$B$25)*4/4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>SUPPLY-CHAIN AUDIT COVERAGE (%) — 2024 → 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13">
+        <f>$B$30+($D$30-$B$30)*0/3</f>
+        <v/>
+      </c>
+      <c r="B32" s="14">
+        <f>$B$30+($D$30-$B$30)*1/3</f>
+        <v/>
+      </c>
+      <c r="C32" s="14">
+        <f>$B$30+($D$30-$B$30)*2/3</f>
+        <v/>
+      </c>
+      <c r="D32" s="13">
+        <f>$B$30+($D$30-$B$30)*3/3</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A20:E21"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A21:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1240,7 +1405,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Annual verification cost (£m)</t>
+          <t>Incremental assurance cost (£m/yr)</t>
         </is>
       </c>
       <c r="D13" s="18" t="n">
@@ -1250,7 +1415,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SPTs met this period (0–3)</t>
+          <t>SPTs met this period (0–3) — scenario input</t>
         </is>
       </c>
       <c r="D14" s="19" t="n">
@@ -1526,7 +1691,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>The commitment fee is identical across scenarios because this structure ratchets only the drawn margin. Some SLLs also ratchet the commitment fee pro rata, which would widen the spread between scenarios by roughly the commitment-fee percentage.</t>
+          <t>The commitment fee is identical across scenarios because this structure ratchets only the drawn margin, and it would be charged on an equivalent conventional revolver too. If the fee were also linked to the margin, the effect would fall on the undrawn balance and so depend on utilisation: at 0% drawn it would be the largest part of the benefit.</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1761,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Verification cost (£k)</t>
+          <t>Incremental assurance (£k)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Net benefit (£k)</t>
+          <t>Net vs conventional (£k)</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1930,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Break-even utilisation</t>
+          <t>Best-case pricing break-even</t>
         </is>
       </c>
       <c r="B14" s="10">
@@ -1774,14 +1939,14 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Below this drawdown the best-case ratchet saving does not cover the verification cost.</t>
+          <t>Below this drawdown the best-case annual saving does not cover the incremental assurance cost, under the model assumptions.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>At the default inputs the break-even is about 21% utilisation. A borrower expecting to keep the facility largely undrawn — which is the normal use of an RCF as a liquidity backstop — gets little or no pricing benefit, and the case for the SLL has to rest on signalling, investor relations or internal accountability rather than on cost. That is a recognised criticism of the instrument and it is worth being explicit about rather than quoting the full-drawdown figure.</t>
+          <t>At the default inputs the best-case annual pricing break-even is about 21% utilisation. It assumes every SPT is met, the whole assurance cost is incremental (already-verified reporting can reduce it), only the drawn margin changes, and there are no other incremental costs. The commitment fee is excluded because an equivalent conventional revolver would charge it too. Where a real borrower would operate is a liquidity question this model does not answer.</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1815,14 +1980,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IS THE STRUCTURE WORTH IT?</t>
+          <t>INCREMENTAL ECONOMICS VS AN EQUIVALENT CONVENTIONAL REVOLVER</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>AT THE DEFAULT INPUTS</t>
+          <t>AT THE DEFAULT INPUTS (commitment fee cancels: charged on both)</t>
         </is>
       </c>
     </row>
@@ -1914,7 +2079,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Annual verification cost</t>
+          <t>Incremental assurance cost</t>
         </is>
       </c>
       <c r="B8" s="14">
@@ -1928,14 +2093,14 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>ISAE 3000 assurance; fixed, does not scale with drawdown</t>
+          <t>Fixed; may be lower where reporting is already verified</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Net annual benefit</t>
+          <t>Net annual benefit vs conventional</t>
         </is>
       </c>
       <c r="B9" s="27">
@@ -1949,17 +2114,17 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Negative means the structure costs more than it returns</t>
+          <t>Negative means the feature costs more than it returns</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Break-even utilisation</t>
-        </is>
-      </c>
-      <c r="B10" s="10">
+          <t>Best-case pricing break-even</t>
+        </is>
+      </c>
+      <c r="B10" s="15">
         <f>'3. Margin Ratchet'!$D$13/('3. Margin Ratchet'!$D$5*'3. Margin Ratchet'!$D$10/100/100)</f>
         <v/>
       </c>
@@ -1970,7 +2135,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Drawdown at which saving = verification cost</t>
+          <t>Drawdown at which best-case saving = assurance cost</t>
         </is>
       </c>
     </row>
@@ -1984,78 +2149,86 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="33" t="inlineStr">
         <is>
-          <t>• The ratchet is priced on the drawn margin only. Structures that also ratchet the commitment fee would show a larger spread.</t>
+          <t>• The ratchet is priced on the drawn margin only. A linked commitment fee would add a benefit on the undrawn balance, largest when least drawn.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="33" t="inlineStr">
         <is>
-          <t>• A ±7.5bps step is small relative to credit-spread volatility, so in practice the SLL label is unlikely to be the binding factor in the borrower's cost of capital.</t>
+          <t>• The pricing grid is unweighted: it counts SPTs met, not which ones, so the carbon target can be missed while a partial step-down is earned.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="33" t="inlineStr">
         <is>
-          <t>• No discounting: these are single-year figures. Over a five-year facility the saving is roughly five times the annual number, less the verification cost each year.</t>
+          <t>• The SPTs are illustrative; alignment with SBTi, CCC or SLLP benchmarks has not been independently established.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="33" t="inlineStr">
         <is>
-          <t>• Verification cost is a single illustrative input. Real assurance costs vary with scope, and the first year is usually dearer than later ones.</t>
+          <t>• No discounting: these are single-year figures. Over a five-year facility the saving is roughly five times the annual number, less the verification cost each year.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="33" t="inlineStr">
         <is>
-          <t>• The two-way ratchet assumes the step-up is genuinely enforced. A step-down-only structure gives the borrower a free option and is the main greenwashing channel the SLLP guidance targets.</t>
+          <t>• Verification cost is a single illustrative input. Real assurance costs vary with scope, and the first year is usually dearer than later ones.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="33" t="inlineStr">
         <is>
+          <t>• The two-way ratchet assumes the step-up is genuinely enforced. A step-down-only structure gives the borrower a free option and is the main greenwashing channel the SLLP guidance targets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
           <t>• KPI selection, not pricing, is where the real integrity risk sits: a material KPI with an unambitious SPT prices identically to a demanding one in this model.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>VERIFICATION &amp; REPORTING</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>External verifier: Big 4 assurance or a specialist ESG verifier. Reporting: annual sustainability report plus a loan anniversary compliance letter. Assurance standard: ISAE 3000 / AA1000AS. KPI data sourced from SECR disclosures (energy and carbon) and the REGO certificate registry (renewable share) — both UK statutory or registry-based, so no paid data subscription is required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>External verifier: an auditor or specialist ESG verifier. Reporting: annual sustainability report plus a loan anniversary compliance letter. Assurance standard: ISAE 3000 / AA1000AS. KPI data sourced from SECR disclosures (energy and carbon) and the REGO certificate registry (renewable share) — both UK statutory or registry-based, so no paid data subscription is required.</t>
+        </is>
+      </c>
+    </row>
     <row r="23"/>
-    <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+    <row r="24"/>
+    <row r="26">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>All figures illustrative — hypothetical borrower, facility and rates.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A21:D23"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A22:D24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
